--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4284,8 +4284,114 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-13T13:22:33</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ZzBsMlNKZTBmNkMweXY5VkFBQUFBQT09OkVzd0JDb3dCUVVwcFZEUjBTMEZ5UWtwdVZGZGtabnBDT0c1RWNqWlNWbWxXUm5WWloyOTBiRTU1U2tSdWJFeHVYMWhJUzFSeE5VVlNWbmRRYURSTFNuUkJXVWxpVkV0aGNsVXdXVGM1YmpOZk5raHROemxHYVZFNFQxaHJVbTB6TkVGcFZVOU5jVjh5YVZkRWJWaHpVV2M0WDNaZmFYRlpPWEpUTUZCeVRIUm5hRTFGWWxwNVZFbEVOSE5qWlRKVFdUTVNGMncyVDIxaGRYcHpSblY2U0hBNE5GQTFPRzFHTmtGUkdpSkJSSE55T1daVVYybzVXak41YVZad2VIRnVlVXRDZEc5RFozbGxSbkJHWWxWMw</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tech Lead Front End / Design System (F/H)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BPCE Solutions informatiques</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>teletravail partiel</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React, Vue.js, Figma, UI, UX</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-08-23T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Offre rejetee: devops pur.</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>55</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>À vérifier: score 55/100 grâce à technologies: frontend, figma, html, css, javascript, react, vue.js, design, design system, web, interface, maquette, accessibilite; titre: front end; domaine_metier: frontend, front end, ui, ux, design, maquette, interface; localisation: dijon; teletravail: teletravail.</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=15; domaine_metier=15; localisation=15; teletravail=10; contrat=0; penalites=35</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React, Vue.js, Figma</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>devops pur</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/tech-lead-front-end-design-system-f-h-at-bpce-solutions-informatiques-4378935390</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB37"/>
+  <autoFilter ref="A1:AB38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4323,6 +4429,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -4315,18 +4315,11 @@
           <t>Dijon, FR</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>À plein temps</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>teletravail partiel</t>
@@ -4345,7 +4338,6 @@
           <t>2026-08-23T00:00:00.000Z</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>Non</t>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AB39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4382,8 +4382,116 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:29:20</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>-3972790397704041599</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Développeur informatique - java/javascript - h/f</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>ATOL CONSEILS ET DEVELOPPEMENTS</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>35k € a 45k €/an</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21T15:05:10.9514360+00:00</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 45/100 grâce à technologies: javascript; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>technologies=15; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-3972790397704041599</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB38"/>
+  <autoFilter ref="A1:AB39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4422,6 +4530,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB39"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4490,8 +4490,120 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:43:20</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>7114434</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Ingénieur(e) Conception et Développement Angular (H/F)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ALTECA</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>21 - Dijon</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>3 An(s)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>HTML, JavaScript</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T04:35:41.635Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23T04:35:41.635Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 56/100 grâce à technologies: html, javascript, digital; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon; teletravail: hybride; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=10; contrat=5; penalites=24</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>HTML, JavaScript</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/7114434</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB39"/>
+  <autoFilter ref="A1:AB40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4531,6 +4643,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -448,7 +448,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="51" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -4602,8 +4602,118 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25T13:55:42</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>5898245281</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Développeur informatique - java/javascript F/H</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>ATOL CONSEILS ET DEVELOPPEMENTS</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>France, Bourgogne-Franche-Comté, Côte-d'Or, Dijon</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>permanent</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>35000 euros - 45000 euros annuel</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:59:57Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 45/100 grâce à technologies: javascript; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>technologies=15; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.fr/details/5898245281?utm_medium=api&amp;utm_source=eb919ca5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB40"/>
+  <autoFilter ref="A1:AB41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4644,6 +4754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4712,8 +4712,108 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26T13:12:52</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>T2lfQ25HdkhwR1gyLWlWbkFBQUFBQT09OkVzd0JDb3dCUVVwcFZEUjBTVlZoZUdKUFpUbDFNRVJWWlcwemFsSnlhMDlLTkdsbGIyMVZXVmxPVG0xdFNHcEhjVXBJU0VwbWEwczJYM0Z2UmpSVVdXNDJSRGN5ZEU1YWFYaENXa1UzTVhsbFVUWkNZM0JWYTJJek0xZEJNSFpLVldWNlgwSm1SV2t3YVhWM2VFTnNkVGhIYTJ4cmQyVmphRFZFTTFOd1IwZFpibVpmWkhGNFNHVmtVV1puVVUxa1ZUVVNGM3BqVXpOaGRrUnNReTF5VHpGelVWQTVORlE1TWtFMEdpSkJSSE55T1daU2RURkJkRzFDVkdOMVYyazFUVVZ4V1Vrd05WZDBjR0ZKVVdwUg</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Ingénieur d'étude informatique H/F</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>JRI</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Belfort, FR</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>HTML, JavaScript</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 56/100 grâce à technologies: html, javascript, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: belfort; teletravail: hybride.</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=8; teletravail=10; contrat=0; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>HTML, JavaScript</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/ing%C3%A9nieur-d-%C3%A9tude-informatique-h-f-at-jri-4467078073</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB41"/>
+  <autoFilter ref="A1:AB42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4755,6 +4855,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AB43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4812,8 +4812,104 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T13:30:32</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>a0ttX3cwVWdHWExwSE1MeEFBQUFBQT09OkVzd0JDb3dCUVVwcFZEUjBTVU4wWHpWVU5rWXhORGRzVDNOUGRuaEVXbFZNYW10clJuUkNiRmxJT1VoVmFFWXhaazVYYTBWYVFVWkRhMnd4VDFOT1oxQXdlbVIxTFZwclluQk1jMnR0VmpWTFJGcHVSV2g2U0VkcVh6QjNkR00xV2pSUWREUm1NMEl6TFVoTE1EVmZSa1pUWkMxTmRHRk5hRFF6VFMwM2FrUlBOalpNUkdnNWVtOWFXakJFTUVGTVlWa1NGMk5SVUVKaGRYWnRSbUpmVURKeWIxQTJPRmhSYTBFNEdpSkJSSE55T1daVVRtRm5WRFIwYW1sVU1tUnljbVpsUVd3NVdtSmxka1pGUzNCMw</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Administrateur exploitation informatique F/H</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>La Poste Groupe</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 60/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/la-poste-groupe/jobs/administrateur-exploitation-informatique-f-h_dijon_LPG_My7GAke</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB42"/>
+  <autoFilter ref="A1:AB43"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4856,6 +4952,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4908,8 +4908,104 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T15:22:45</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>-847835290928670758</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Conseiller(ère) informatique support client</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>SG2i</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Apollinaire, Côte-d'Or</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Intérimaire</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T10:46:39.8763370+00:00</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 60/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: saint-apollinaire.</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-847835290928670758</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB43"/>
+  <autoFilter ref="A1:AB44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4953,6 +5049,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5004,8 +5004,118 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10T14:32:29</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>5896041402</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Développeur Informatique - Java - Javascript H/F</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Atol Conseils et développements</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>France, Bourgogne-Franche-Comté, Côte-d'Or, Dijon</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>35000 euros - 45000 euros annuel</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24T03:14:15Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 45/100 grâce à technologies: javascript; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>technologies=15; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.fr/details/5896041402?utm_medium=api&amp;utm_source=eb919ca5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB44"/>
+  <autoFilter ref="A1:AB45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5050,6 +5160,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5114,8 +5114,226 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11T14:58:57</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>7841278</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>UX / UI DESIGNER - H/F</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ATOL CONSEILS ET DEVELOPPEMENTS</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>21 - Dijon</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2 An(s)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Annuel de 35000.0 Euros à 40000.0 Euros</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>37500</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:36:15.502Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10T19:36:15.502Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 95/100 grâce à technologies: ui designer, ux designer, digital, design, interface, maquette; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme, maquette, interface; localisation: dijon; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=5</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>UI designer, UX designer</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/7841278</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11T14:59:00</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>-5455197705641820853</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Développeur Full Stack F/H (CDI)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Golden Bees</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, TypeScript</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10T20:54:14.2989074+00:00</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 65/100 grâce à technologies: front-end, html, css, javascript; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-5455197705641820853</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB45"/>
+  <autoFilter ref="A1:AB47"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5161,6 +5379,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB47"/>
+  <dimension ref="A1:AB48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5332,8 +5332,136 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:31:32</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>215GGHD</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Consultant(e) Fonctionnel(le) Digitalisation Industrielle (H/F)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>DYMASCO</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>21 - Salives</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>21580</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>3 An(s)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Annuel de 40000.0 Euros à 45000.0 Euros</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>42500</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>teletravail partiel</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T18:00:02.697Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T18:00:02.697Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 77/100 grâce à technologies: html, css, javascript, digital, interface; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme, interface; localisation: departement 21; teletravail: teletravail, jours_teletravail; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=12; teletravail=10; contrat=5</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/215GGHD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB47"/>
+  <autoFilter ref="A1:AB48"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5381,6 +5509,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5460,8 +5460,120 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T15:43:30</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>8042246</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Ingénieur(e) Conception et Développement Angular (H/F)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ALTECA</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>21 - Dijon</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>3 An(s)</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>HTML, JavaScript</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T04:31:54.600Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T04:31:54.600Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 56/100 grâce à technologies: html, javascript, digital; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon; teletravail: hybride; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=10; contrat=5; penalites=24</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>HTML, JavaScript</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/8042246</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB48"/>
+  <autoFilter ref="A1:AB49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5510,6 +5622,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5572,8 +5572,110 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T15:18:25</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ZU4zeFN4V1BoWU12LU5PNEFBQUFBQT09OkVzd0JDb3dCUVVSRVlsZGxZbVpWYldWcFpIZHljMHBJTjA5NFREVk1ZMHBvTkhSb1dGUlVTM0ZSYzJOdGRXTndjVE5yT0ZFdE5HcHJiVmsyUWw5alpFRlhaazFZYVhsdE15MUZhbmcwU0ZVdFMxWlRiM1Z3U0ZOb05ISjJRbWRzWlV3d1FUbE5jVkpGVjNWbWIwSmpZbnAxYlhZMFEzazBkMFp0U1hWYU1VOURTblpXYWtkVlZrVlVUV1Z1TVZSUFNTMFNGM1p0VUdwaGRqWnFRMjgzVFd0UVNWQjFTbWxLTmtGVkdpSkJTRTR3UlRkRmVYZDNZbFoyTkdkaE5GQmhUR052UWtKdlkxRlNXR05RU3pobg</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Analyste développeur</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>JobScanner</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>teletravail partiel</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 58/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon; teletravail: teletravail, jours_teletravail.</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=10; contrat=0; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-28656-a481673f3ffe4d5213f173dcd6d10ff2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB49"/>
+  <autoFilter ref="A1:AB50"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5623,6 +5725,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB50"/>
+  <dimension ref="A1:AB52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5674,8 +5674,206 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T15:07:38</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>bE9pNGpyMDBIUjJSdWo5SEFBQUFBQT09OkVzc0JDb3dCUVVSRVlsZGxZVkI2TjNSNFJrVjVTbmhoVjBSdFNUVlVkVzF6TVZKUlkyaFFlRXR4VTAxaGQzaGpWMlJ1TW5adFkyNDJkRUp4T1ZSR1JuVTNWRWczVFdwWmNWVTNOak5zYjFKc1Z6TldlRlJ2YTNOMmFtTnBZekV0Y2twMlVUUnBZMFJJY3psaExVVkhPVkV6ZG5aRFQya3dUWGRQYTNVNWFteERVbXBXWjJkU2IwbE1SMG8xVkhNdE1USVNGbk55VEd0aGRGTllRMDlYZERWT2IxQnROMFJDUjBFYUlrRklUakJGTjBaTVQzWXlhVUpGUVVjMmFtcEhaSHB0WmxwclpHWkZVSGx5ZW1j</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Développeur – Coordinateur informatique H/F</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Fonction publique Territoriale</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Besançon, FR</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 46/100 grâce à technologies: html, css, javascript, react, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: besancon.</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=8; teletravail=0; contrat=0; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-4025-6899989d567587bea62c9ea716e836fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T15:07:38</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ZU4zeFN4V1BoWU12LU5PNEFBQUFBQT09OkVzd0JDb3dCUVVSRVlsZGxZbUoxWVd4alZtZzFZM0kyV2tWRmFFcFVZMnBNT1RWUlVtdFlka2hTZWxGU1VXbFNlWEozZGpKUFgyOTBOaTFmVDE5bVpsTklWRzltYVVJNWIyeE5Na2x5YUVaTk5sQk1SMnQwV1RZd01uWnJkMHMyYzAxUFJIYzJYMXBZUmxwRlJrZHlabVJDWkdKR1NqaDVlWEJGYm1GNU0wOW9kMFUzVTFoUE9EZFZaMU5YUW14V09EUVNGM1EzVEd0aGIzVlNUVGRtWXpKeWIxQnpjM1ZyTFVGVkdpSkJTRTR3UlRkSWJHOVBlVlJVTmxJeFpGbHZaVmx2WWtnM2NtVmZla1Z6Y0hsQg</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Analyste développeur</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>JobScanner</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>teletravail partiel</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 58/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon; teletravail: teletravail, jours_teletravail.</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=10; contrat=0; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-28656-a481673f3ffe4d5213f173dcd6d10ff2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB50"/>
+  <autoFilter ref="A1:AB52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5726,6 +5924,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB52"/>
+  <dimension ref="A1:AB53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5872,8 +5872,104 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31T14:36:25</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>bE9pNGpyMDBIUjJSdWo5SEFBQUFBQT09OkVzc0JDb3dCUVVSRVlsZGxXVGd5WkhnMFdubHJWMUJIVFhaRGNtUnhiVFkxWTA1dmJUWktlVjh3UW5wdFdqUmxTa0l0WlZCdmNtZDBRMVJZY1RGWGRIUm5WakpxVFVGYVp6ZHVaVTlWVlU1Qk1tNVhjRlkyTWw5bGJVZERlRE5MUms1emVubEdUa010WjNjdGJIVTJjMWRpVTJsZmFTMVdhVEZRUTJSc2FtUXhVbWROVDJNMk1uZHBRbGRRU1VkUllWUVNGak5mZW14aGMzWXhURGhwYTJsTVRWQjVPRGRyV1ZFYUlrRklUakJGTjBkQmNreDBSSFo2V1hoNlgyWjNUV0pqU0VGQll6QmlRblpMZDNj</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Développeur – Coordinateur informatique H/F</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Fonction publique Territoriale</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Besançon, FR</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 46/100 grâce à technologies: html, css, javascript, react, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: besancon.</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=8; teletravail=0; contrat=0; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-4025-6899989d567587bea62c9ea716e836fc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB52"/>
+  <autoFilter ref="A1:AB53"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -5926,6 +6022,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
